--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98706862</v>
+        <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100011</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Omkring Noppikoski, Dlr</t>
+          <t>Källmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492694</v>
+        <v>492868</v>
       </c>
       <c r="R2" t="n">
-        <v>6820802</v>
+        <v>6820649</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Aphåll FLD0008a (Calluna AB) örninventering</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,24 +775,608 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>John Kvarnbäck</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137187907</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>98706862</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Omkring Noppikoski, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>492694</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6820802</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Aphåll FLD0008a (Calluna AB) örninventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>John Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/98706862</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137189262</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Källmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492815</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6820637</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Uppflog Noterar enstaka gråalsbuketter inom anmälan, en förutsättning för järpe</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189262</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137188176</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Koskuso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>492682</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6820824</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137188176</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137187824</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Källmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492850</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6820602</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137187824</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137187940</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Källmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492861</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6820661</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137187940</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137189262</v>
       </c>
       <c r="B4" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137188176</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137189262</v>
       </c>
       <c r="B4" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137188176</v>
       </c>
       <c r="B5" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137187824</v>
       </c>
       <c r="B6" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137187940</v>
       </c>
       <c r="B7" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137189262</v>
       </c>
       <c r="B4" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137188176</v>
       </c>
       <c r="B5" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137187824</v>
       </c>
       <c r="B6" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137187940</v>
       </c>
       <c r="B7" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137189262</v>
       </c>
       <c r="B4" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137188176</v>
       </c>
       <c r="B5" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137188176</v>
       </c>
       <c r="B5" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40041-2026 artfynd.xlsx
+++ b/artfynd/A 40041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137187907</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137189262</v>
       </c>
       <c r="B4" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137188176</v>
       </c>
       <c r="B5" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
